--- a/artfynd/A 25470-2026 artfynd.xlsx
+++ b/artfynd/A 25470-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136012394</v>
       </c>
       <c r="B2" t="n">
-        <v>97513</v>
+        <v>97530</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136012734</v>
       </c>
       <c r="B3" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136012722</v>
       </c>
       <c r="B4" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 25470-2026 artfynd.xlsx
+++ b/artfynd/A 25470-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136012394</v>
       </c>
       <c r="B2" t="n">
-        <v>97530</v>
+        <v>97531</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136012734</v>
       </c>
       <c r="B3" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136012722</v>
       </c>
       <c r="B4" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 25470-2026 artfynd.xlsx
+++ b/artfynd/A 25470-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136012394</v>
       </c>
       <c r="B2" t="n">
-        <v>97531</v>
+        <v>97532</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25470-2026 artfynd.xlsx
+++ b/artfynd/A 25470-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136012394</v>
       </c>
       <c r="B2" t="n">
-        <v>97532</v>
+        <v>97533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136012734</v>
       </c>
       <c r="B3" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136012722</v>
       </c>
       <c r="B4" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 25470-2026 artfynd.xlsx
+++ b/artfynd/A 25470-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136012394</v>
       </c>
       <c r="B2" t="n">
-        <v>97533</v>
+        <v>97539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136012734</v>
       </c>
       <c r="B3" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136012722</v>
       </c>
       <c r="B4" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 25470-2026 artfynd.xlsx
+++ b/artfynd/A 25470-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136012394</v>
       </c>
       <c r="B2" t="n">
-        <v>97539</v>
+        <v>97540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136012734</v>
       </c>
       <c r="B3" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136012722</v>
       </c>
       <c r="B4" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 25470-2026 artfynd.xlsx
+++ b/artfynd/A 25470-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136012394</v>
       </c>
       <c r="B2" t="n">
-        <v>97540</v>
+        <v>97551</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136012734</v>
       </c>
       <c r="B3" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136012722</v>
       </c>
       <c r="B4" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 25470-2026 artfynd.xlsx
+++ b/artfynd/A 25470-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136012394</v>
       </c>
       <c r="B2" t="n">
-        <v>97551</v>
+        <v>97564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136012734</v>
       </c>
       <c r="B3" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136012722</v>
       </c>
       <c r="B4" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 25470-2026 artfynd.xlsx
+++ b/artfynd/A 25470-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136012394</v>
       </c>
       <c r="B2" t="n">
-        <v>97564</v>
+        <v>97565</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25470-2026 artfynd.xlsx
+++ b/artfynd/A 25470-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136012394</v>
       </c>
       <c r="B2" t="n">
-        <v>97565</v>
+        <v>97578</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136012734</v>
       </c>
       <c r="B3" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136012722</v>
       </c>
       <c r="B4" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 25470-2026 artfynd.xlsx
+++ b/artfynd/A 25470-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136012394</v>
       </c>
       <c r="B2" t="n">
-        <v>97578</v>
+        <v>97579</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136012734</v>
       </c>
       <c r="B3" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136012722</v>
       </c>
       <c r="B4" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
